--- a/assets/data/松下新风功能对比表.xlsx
+++ b/assets/data/松下新风功能对比表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\waipc\Documents\GitHub\songxiaxinfeng\sources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\waipc\Documents\GitHub\songxiaxinfeng\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAD82A4-DA62-454A-A90F-9337ECDF82E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C328697-8C68-4889-9AF6-307B7D09DCDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="214" yWindow="154" windowWidth="19183" windowHeight="11263" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="新风" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="91">
   <si>
     <t>产品系列</t>
   </si>
@@ -133,9 +133,6 @@
     <t>保修期</t>
   </si>
   <si>
-    <t>全国联保，整机3年，马达8年</t>
-  </si>
-  <si>
     <t>设备参数</t>
   </si>
   <si>
@@ -167,9 +164,6 @@
   </si>
   <si>
     <t>FV-25ZM2C</t>
-  </si>
-  <si>
-    <t>FV-35ZM2C</t>
   </si>
   <si>
     <t>适用面积</t>
@@ -277,10 +271,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>除湿量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>50-100</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -301,14 +291,46 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">备注：
+    <t>●</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZY系列</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FV-35ZM2C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FY-15ZY1C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FY-25ZY1C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FY-35ZY1C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FY-50ZY1C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>除湿量*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">*
 1. 除湿全热类设备的除湿量测试工况为：室内27℃，50%相对湿度，室外35℃，60%相对湿度。
 2. 除湿新风类设备的除湿量测试工况为：室内30℃，80%相对湿度。
 </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>●</t>
+    <t>全国联保，整机1年，马达8年，压缩机3年，电路板3年</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -345,7 +367,7 @@
       <patternFill patternType="none"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -412,13 +434,96 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -452,6 +557,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -465,6 +576,42 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -722,7 +869,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z37"/>
+  <dimension ref="A1:Z56"/>
   <sheetFormatPr defaultColWidth="13.86328125" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.6640625" style="5"/>
@@ -733,234 +880,290 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="10" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="10" t="s">
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="10" t="s">
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
       <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
+      <c r="G2" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="13"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="26"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="12" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
+      <c r="C3" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="13"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="11"/>
+      <c r="A4" s="13"/>
       <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
+      <c r="C4" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4" s="12"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="11"/>
+      <c r="A5" s="13"/>
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
+      <c r="C5" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" s="12"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="11"/>
+      <c r="A6" s="13"/>
       <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
+      <c r="C6" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="K6" s="12"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="11"/>
+      <c r="A7" s="13"/>
       <c r="B7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
+      <c r="C7" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="12"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
     </row>
     <row r="8" spans="1:26" ht="18" customHeight="1">
-      <c r="A8" s="11"/>
+      <c r="A8" s="13"/>
       <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
+      <c r="C8" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="12"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
     </row>
     <row r="9" spans="1:26" ht="18" customHeight="1">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="12" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10" t="s">
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10" t="s">
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
     </row>
     <row r="10" spans="1:26" ht="18" customHeight="1">
-      <c r="A10" s="11"/>
+      <c r="A10" s="13"/>
       <c r="B10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
+      <c r="C10" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="K10" s="12"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
@@ -973,30 +1176,32 @@
       <c r="Z10" s="2"/>
     </row>
     <row r="11" spans="1:26" ht="18" customHeight="1">
-      <c r="A11" s="11"/>
+      <c r="A11" s="13"/>
       <c r="B11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
+      <c r="C11" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="K11" s="12"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
@@ -1009,391 +1214,497 @@
       <c r="Z11" s="2"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="10"/>
+      <c r="A12" s="12"/>
       <c r="B12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
+      <c r="C12" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="K12" s="12"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
     </row>
     <row r="13" spans="1:26" ht="18" customHeight="1">
-      <c r="A13" s="10"/>
+      <c r="A13" s="12"/>
       <c r="B13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
+      <c r="C13" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="K13" s="12"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
     </row>
     <row r="14" spans="1:26" ht="18" customHeight="1">
-      <c r="A14" s="10"/>
+      <c r="A14" s="12"/>
       <c r="B14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
+      <c r="C14" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="K14" s="12"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
     </row>
     <row r="15" spans="1:26" ht="18" customHeight="1">
-      <c r="A15" s="10"/>
+      <c r="A15" s="12"/>
       <c r="B15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
+      <c r="C15" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="K15" s="12"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
     </row>
     <row r="16" spans="1:26" ht="18" customHeight="1">
-      <c r="A16" s="11"/>
+      <c r="A16" s="13"/>
       <c r="B16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
+      <c r="C16" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="K16" s="12"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="12"/>
     </row>
     <row r="17" spans="1:26" ht="18" customHeight="1">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="12" t="s">
         <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
+      <c r="C17" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="K17" s="13"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
     </row>
     <row r="18" spans="1:26" ht="18" customHeight="1">
-      <c r="A18" s="11"/>
+      <c r="A18" s="13"/>
       <c r="B18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
+      <c r="C18" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="K18" s="12"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
     </row>
     <row r="19" spans="1:26" ht="18" customHeight="1">
-      <c r="A19" s="11"/>
+      <c r="A19" s="13"/>
       <c r="B19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
+      <c r="C19" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="K19" s="12"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13"/>
     </row>
     <row r="20" spans="1:26" ht="18" customHeight="1">
-      <c r="A20" s="11"/>
+      <c r="A20" s="13"/>
       <c r="B20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
+      <c r="C20" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="K20" s="12"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N20" s="12"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="12"/>
     </row>
     <row r="21" spans="1:26" ht="16.3">
-      <c r="A21" s="11"/>
+      <c r="A21" s="13"/>
       <c r="B21" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
+      <c r="C21" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="K21" s="12"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N21" s="12"/>
+      <c r="O21" s="12"/>
+      <c r="P21" s="12"/>
     </row>
     <row r="22" spans="1:26" ht="16.3">
-      <c r="A22" s="11"/>
+      <c r="A22" s="13"/>
       <c r="B22" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
+      <c r="C22" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="K22" s="12"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N22" s="12"/>
+      <c r="O22" s="12"/>
+      <c r="P22" s="12"/>
     </row>
     <row r="23" spans="1:26" ht="16.3">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="12" t="s">
         <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
+      <c r="C23" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="K23" s="12"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13"/>
+      <c r="P23" s="13"/>
     </row>
     <row r="24" spans="1:26" ht="16.3">
-      <c r="A24" s="11"/>
+      <c r="A24" s="13"/>
       <c r="B24" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
+      <c r="C24" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="K24" s="12"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N24" s="12"/>
+      <c r="O24" s="12"/>
+      <c r="P24" s="12"/>
     </row>
     <row r="25" spans="1:26" ht="16.3">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="10" t="s">
+      <c r="B25" s="15"/>
+      <c r="C25" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="28"/>
+      <c r="N25" s="28"/>
+      <c r="O25" s="28"/>
+      <c r="P25" s="29"/>
+    </row>
+    <row r="26" spans="1:26" ht="16.3">
+      <c r="A26" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-    </row>
-    <row r="26" spans="1:26" ht="16.3">
-      <c r="A26" s="10" t="s">
+      <c r="B26" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="E26" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="F26" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="G26" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="H26" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="I26" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="J26" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="K26" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="L26" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="M26" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="N26" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="O26" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="P26" s="21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" ht="16.3">
+      <c r="A27" s="12"/>
+      <c r="B27" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L26" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="27" spans="1:26" ht="16.3">
-      <c r="A27" s="10"/>
-      <c r="B27" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="E27" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="G27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="M27" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="N27" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="O27" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="P27" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" ht="16.3">
+      <c r="A28" s="13"/>
+      <c r="B28" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:26" ht="16.3">
-      <c r="A28" s="11"/>
-      <c r="B28" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="C28" s="1">
         <v>250</v>
@@ -1422,14 +1733,26 @@
       <c r="K28" s="1">
         <v>250</v>
       </c>
-      <c r="L28" s="1">
+      <c r="L28" s="11">
         <v>350</v>
       </c>
+      <c r="M28" s="10">
+        <v>150</v>
+      </c>
+      <c r="N28" s="10">
+        <v>250</v>
+      </c>
+      <c r="O28" s="10">
+        <v>350</v>
+      </c>
+      <c r="P28" s="10">
+        <v>500</v>
+      </c>
     </row>
     <row r="29" spans="1:26" ht="16.3">
-      <c r="A29" s="11"/>
+      <c r="A29" s="13"/>
       <c r="B29" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C29" s="1">
         <v>150</v>
@@ -1458,14 +1781,26 @@
       <c r="K29" s="1">
         <v>110</v>
       </c>
-      <c r="L29" s="1">
+      <c r="L29" s="11">
         <v>130</v>
       </c>
+      <c r="M29" s="21">
+        <v>100</v>
+      </c>
+      <c r="N29" s="21">
+        <v>120</v>
+      </c>
+      <c r="O29" s="21">
+        <v>140</v>
+      </c>
+      <c r="P29" s="21">
+        <v>130</v>
+      </c>
     </row>
     <row r="30" spans="1:26" ht="16.3">
-      <c r="A30" s="11"/>
+      <c r="A30" s="13"/>
       <c r="B30" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C30" s="1">
         <v>105</v>
@@ -1494,14 +1829,26 @@
       <c r="K30" s="1">
         <v>96</v>
       </c>
-      <c r="L30" s="1">
+      <c r="L30" s="11">
         <v>144</v>
       </c>
+      <c r="M30" s="21">
+        <v>76</v>
+      </c>
+      <c r="N30" s="21">
+        <v>106</v>
+      </c>
+      <c r="O30" s="21">
+        <v>141</v>
+      </c>
+      <c r="P30" s="21">
+        <v>180</v>
+      </c>
     </row>
     <row r="31" spans="1:26" s="5" customFormat="1" ht="16.3">
-      <c r="A31" s="11"/>
+      <c r="A31" s="13"/>
       <c r="B31" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C31" s="3">
         <v>0.67</v>
@@ -1530,14 +1877,22 @@
       <c r="K31" s="3">
         <v>0.59</v>
       </c>
-      <c r="L31" s="3">
+      <c r="L31" s="19">
         <v>0.59</v>
       </c>
-      <c r="M31" s="2"/>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
-      <c r="P31" s="2"/>
-      <c r="Q31" s="2"/>
+      <c r="M31" s="22">
+        <v>59</v>
+      </c>
+      <c r="N31" s="22">
+        <v>59</v>
+      </c>
+      <c r="O31" s="22">
+        <v>61</v>
+      </c>
+      <c r="P31" s="22">
+        <v>59</v>
+      </c>
+      <c r="Q31"/>
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
       <c r="T31" s="2"/>
@@ -1549,9 +1904,9 @@
       <c r="Z31" s="2"/>
     </row>
     <row r="32" spans="1:26" ht="16.3">
-      <c r="A32" s="11"/>
+      <c r="A32" s="13"/>
       <c r="B32" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C32" s="3">
         <v>0.74</v>
@@ -1580,14 +1935,27 @@
       <c r="K32" s="3">
         <v>0.65</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="19">
         <v>0.65</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" ht="16.3">
-      <c r="A33" s="11"/>
+      <c r="M32" s="21">
+        <v>69</v>
+      </c>
+      <c r="N32" s="21">
+        <v>69</v>
+      </c>
+      <c r="O32" s="21">
+        <v>75</v>
+      </c>
+      <c r="P32" s="21">
+        <v>68</v>
+      </c>
+      <c r="Q32"/>
+    </row>
+    <row r="33" spans="1:17" ht="16.3">
+      <c r="A33" s="13"/>
       <c r="B33" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C33" s="1">
         <v>33</v>
@@ -1616,14 +1984,27 @@
       <c r="K33" s="1">
         <v>34</v>
       </c>
-      <c r="L33" s="1">
+      <c r="L33" s="11">
         <v>36</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" ht="16.3">
-      <c r="A34" s="11"/>
+      <c r="M33" s="21">
+        <v>37</v>
+      </c>
+      <c r="N33" s="21">
+        <v>38</v>
+      </c>
+      <c r="O33" s="21">
+        <v>39</v>
+      </c>
+      <c r="P33" s="21">
+        <v>43</v>
+      </c>
+      <c r="Q33"/>
+    </row>
+    <row r="34" spans="1:17" ht="16.3">
+      <c r="A34" s="13"/>
       <c r="B34" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C34" s="4">
         <v>46</v>
@@ -1652,14 +2033,27 @@
       <c r="K34" s="4">
         <v>26</v>
       </c>
-      <c r="L34" s="4">
+      <c r="L34" s="20">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" ht="16.3">
-      <c r="A35" s="11"/>
+      <c r="M34" s="21">
+        <v>23</v>
+      </c>
+      <c r="N34" s="21">
+        <v>27</v>
+      </c>
+      <c r="O34" s="21">
+        <v>37</v>
+      </c>
+      <c r="P34" s="21">
+        <v>40</v>
+      </c>
+      <c r="Q34"/>
+    </row>
+    <row r="35" spans="1:17" ht="16.3">
+      <c r="A35" s="13"/>
       <c r="B35" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C35" s="4">
         <v>950</v>
@@ -1688,14 +2082,27 @@
       <c r="K35" s="4">
         <v>560</v>
       </c>
-      <c r="L35" s="4">
+      <c r="L35" s="20">
         <v>735</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" ht="16.3">
-      <c r="A36" s="11"/>
+      <c r="M35" s="21">
+        <v>860</v>
+      </c>
+      <c r="N35" s="21">
+        <v>860</v>
+      </c>
+      <c r="O35" s="21">
+        <v>968</v>
+      </c>
+      <c r="P35" s="21">
+        <v>968</v>
+      </c>
+      <c r="Q35"/>
+    </row>
+    <row r="36" spans="1:17" ht="16.3">
+      <c r="A36" s="13"/>
       <c r="B36" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C36" s="4">
         <v>880</v>
@@ -1724,14 +2131,27 @@
       <c r="K36" s="4">
         <v>660</v>
       </c>
-      <c r="L36" s="4">
+      <c r="L36" s="20">
         <v>705</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" ht="16.3">
-      <c r="A37" s="11"/>
+      <c r="M36" s="21">
+        <v>610</v>
+      </c>
+      <c r="N36" s="21">
+        <v>735</v>
+      </c>
+      <c r="O36" s="21">
+        <v>874</v>
+      </c>
+      <c r="P36" s="21">
+        <v>1016</v>
+      </c>
+      <c r="Q36"/>
+    </row>
+    <row r="37" spans="1:17" ht="16.3">
+      <c r="A37" s="13"/>
       <c r="B37" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C37" s="4">
         <v>250</v>
@@ -1760,77 +2180,107 @@
       <c r="K37" s="4">
         <v>220</v>
       </c>
-      <c r="L37" s="4">
+      <c r="L37" s="20">
         <v>230</v>
       </c>
+      <c r="M37" s="21">
+        <v>289</v>
+      </c>
+      <c r="N37" s="21">
+        <v>289</v>
+      </c>
+      <c r="O37" s="21">
+        <v>331</v>
+      </c>
+      <c r="P37" s="21">
+        <v>331</v>
+      </c>
+      <c r="Q37"/>
+    </row>
+    <row r="38" spans="1:17" ht="18" customHeight="1">
+      <c r="Q38"/>
+    </row>
+    <row r="39" spans="1:17" ht="18" customHeight="1">
+      <c r="Q39"/>
+    </row>
+    <row r="40" spans="1:17" ht="18" customHeight="1">
+      <c r="Q40"/>
+    </row>
+    <row r="41" spans="1:17" ht="18" customHeight="1">
+      <c r="Q41"/>
+    </row>
+    <row r="42" spans="1:17" ht="18" customHeight="1">
+      <c r="Q42"/>
+    </row>
+    <row r="43" spans="1:17" ht="18" customHeight="1">
+      <c r="Q43"/>
+    </row>
+    <row r="44" spans="1:17" ht="18" customHeight="1">
+      <c r="Q44"/>
+    </row>
+    <row r="45" spans="1:17" ht="18" customHeight="1">
+      <c r="Q45"/>
+    </row>
+    <row r="46" spans="1:17" ht="18" customHeight="1">
+      <c r="Q46"/>
+    </row>
+    <row r="47" spans="1:17" ht="18" customHeight="1">
+      <c r="Q47"/>
+    </row>
+    <row r="48" spans="1:17" ht="18" customHeight="1">
+      <c r="Q48"/>
+    </row>
+    <row r="49" spans="17:17" ht="18" customHeight="1">
+      <c r="Q49"/>
+    </row>
+    <row r="50" spans="17:17" ht="18" customHeight="1">
+      <c r="Q50"/>
+    </row>
+    <row r="51" spans="17:17" ht="18" customHeight="1">
+      <c r="Q51"/>
+    </row>
+    <row r="52" spans="17:17" ht="18" customHeight="1">
+      <c r="Q52"/>
+    </row>
+    <row r="53" spans="17:17" ht="18" customHeight="1">
+      <c r="Q53"/>
+    </row>
+    <row r="54" spans="17:17" ht="18" customHeight="1">
+      <c r="Q54"/>
+    </row>
+    <row r="55" spans="17:17" ht="18" customHeight="1">
+      <c r="Q55"/>
+    </row>
+    <row r="56" spans="17:17" ht="18" customHeight="1">
+      <c r="Q56"/>
     </row>
   </sheetData>
-  <mergeCells count="81">
-    <mergeCell ref="A26:A37"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A9:A16"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="A17:A22"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="J24:L24"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="J18:L18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="J20:L20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="J21:L21"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="J8:L8"/>
+  <mergeCells count="105">
+    <mergeCell ref="M21:P21"/>
+    <mergeCell ref="M22:P22"/>
+    <mergeCell ref="M23:P23"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="C25:P25"/>
+    <mergeCell ref="M16:P16"/>
+    <mergeCell ref="M17:P17"/>
+    <mergeCell ref="M18:P18"/>
+    <mergeCell ref="M19:P19"/>
+    <mergeCell ref="M20:P20"/>
+    <mergeCell ref="M11:P11"/>
+    <mergeCell ref="M12:P12"/>
+    <mergeCell ref="M13:P13"/>
+    <mergeCell ref="M14:P14"/>
+    <mergeCell ref="M15:P15"/>
+    <mergeCell ref="M6:P6"/>
+    <mergeCell ref="M7:P7"/>
+    <mergeCell ref="M8:P8"/>
+    <mergeCell ref="M9:P9"/>
+    <mergeCell ref="M10:P10"/>
+    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="M3:P3"/>
+    <mergeCell ref="M4:P4"/>
+    <mergeCell ref="M5:P5"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="F1:I1"/>
@@ -1847,6 +2297,70 @@
     <mergeCell ref="F15:I15"/>
     <mergeCell ref="J15:L15"/>
     <mergeCell ref="F13:I13"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="J21:L21"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="J18:L18"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="J24:L24"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="A26:A37"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A9:A16"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="A17:A22"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1868,43 +2382,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="18" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="14"/>
-      <c r="E1" s="12" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="16"/>
+      <c r="E1" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="16"/>
+      <c r="G1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="14"/>
-      <c r="G1" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>66</v>
-      </c>
     </row>
     <row r="2" spans="1:15" s="7" customFormat="1" ht="18" customHeight="1">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="16"/>
+      <c r="E2" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="16"/>
+      <c r="G2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" s="14"/>
-      <c r="G2" s="6" t="s">
-        <v>72</v>
-      </c>
       <c r="H2" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
@@ -1915,18 +2429,18 @@
       <c r="O2" s="5"/>
     </row>
     <row r="3" spans="1:15" ht="18" customHeight="1">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="14"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="16"/>
+      <c r="E3" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="16"/>
       <c r="G3" s="6" t="s">
         <v>5</v>
       </c>
@@ -1935,20 +2449,20 @@
       </c>
     </row>
     <row r="4" spans="1:15" ht="18" customHeight="1">
-      <c r="A4" s="10" t="s">
-        <v>74</v>
+      <c r="A4" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="14"/>
+      <c r="C4" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="16"/>
+      <c r="E4" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="16"/>
       <c r="G4" s="6" t="s">
         <v>5</v>
       </c>
@@ -1957,38 +2471,38 @@
       </c>
     </row>
     <row r="5" spans="1:15" ht="18" customHeight="1">
-      <c r="A5" s="10"/>
+      <c r="A5" s="12"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="F5" s="14"/>
+      <c r="C5" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="16"/>
+      <c r="E5" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F5" s="16"/>
       <c r="G5" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1">
-      <c r="A6" s="10"/>
+      <c r="A6" s="12"/>
       <c r="B6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="14"/>
+      <c r="C6" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="16"/>
+      <c r="E6" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="16"/>
       <c r="G6" s="8" t="s">
         <v>6</v>
       </c>
@@ -1997,40 +2511,40 @@
       </c>
     </row>
     <row r="7" spans="1:15" ht="18" customHeight="1">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="12" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="12" t="s">
+      <c r="D7" s="16"/>
+      <c r="E7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="14"/>
+      <c r="F7" s="16"/>
       <c r="G7" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:15" s="7" customFormat="1" ht="18" customHeight="1">
-      <c r="A8" s="10"/>
+      <c r="A8" s="12"/>
       <c r="B8" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="14"/>
+        <v>71</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="16"/>
+      <c r="E8" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="16"/>
       <c r="G8" s="6" t="s">
         <v>6</v>
       </c>
@@ -2046,18 +2560,18 @@
       <c r="O8" s="5"/>
     </row>
     <row r="9" spans="1:15" ht="18" customHeight="1">
-      <c r="A9" s="11"/>
+      <c r="A9" s="13"/>
       <c r="B9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="14"/>
+      <c r="C9" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="16"/>
+      <c r="E9" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="16"/>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
@@ -2073,18 +2587,18 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="18" customHeight="1">
-      <c r="A10" s="11"/>
+      <c r="A10" s="13"/>
       <c r="B10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="14"/>
+      <c r="C10" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="16"/>
+      <c r="E10" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="16"/>
       <c r="G10" s="6" t="s">
         <v>5</v>
       </c>
@@ -2100,18 +2614,18 @@
       <c r="O10" s="2"/>
     </row>
     <row r="11" spans="1:15" ht="18" customHeight="1">
-      <c r="A11" s="10"/>
+      <c r="A11" s="12"/>
       <c r="B11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" s="14"/>
+      <c r="C11" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="16"/>
+      <c r="E11" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="16"/>
       <c r="G11" s="6" t="s">
         <v>5</v>
       </c>
@@ -2120,18 +2634,18 @@
       </c>
     </row>
     <row r="12" spans="1:15" ht="18" customHeight="1">
-      <c r="A12" s="10"/>
+      <c r="A12" s="12"/>
       <c r="B12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" s="14"/>
+      <c r="C12" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="16"/>
+      <c r="E12" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="16"/>
       <c r="G12" s="6" t="s">
         <v>6</v>
       </c>
@@ -2140,18 +2654,18 @@
       </c>
     </row>
     <row r="13" spans="1:15" ht="18" customHeight="1">
-      <c r="A13" s="10"/>
+      <c r="A13" s="12"/>
       <c r="B13" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="14"/>
+      <c r="C13" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="16"/>
+      <c r="E13" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="16"/>
       <c r="G13" s="6" t="s">
         <v>6</v>
       </c>
@@ -2160,18 +2674,18 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="18" customHeight="1">
-      <c r="A14" s="10"/>
+      <c r="A14" s="12"/>
       <c r="B14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" s="14"/>
+      <c r="C14" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="16"/>
+      <c r="E14" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="16"/>
       <c r="G14" s="6" t="s">
         <v>6</v>
       </c>
@@ -2180,18 +2694,18 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="18" customHeight="1">
-      <c r="A15" s="11"/>
+      <c r="A15" s="13"/>
       <c r="B15" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="14"/>
+      <c r="C15" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="16"/>
+      <c r="E15" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="16"/>
       <c r="G15" s="6" t="s">
         <v>5</v>
       </c>
@@ -2200,20 +2714,20 @@
       </c>
     </row>
     <row r="16" spans="1:15" ht="18" customHeight="1">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="12" t="s">
         <v>24</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" s="14"/>
+      <c r="C16" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="16"/>
+      <c r="E16" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" s="16"/>
       <c r="G16" s="6" t="s">
         <v>6</v>
       </c>
@@ -2222,18 +2736,18 @@
       </c>
     </row>
     <row r="17" spans="1:15" ht="18" customHeight="1">
-      <c r="A17" s="11"/>
+      <c r="A17" s="13"/>
       <c r="B17" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" s="14"/>
-      <c r="E17" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" s="14"/>
+      <c r="C17" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="16"/>
+      <c r="E17" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="16"/>
       <c r="G17" s="6" t="s">
         <v>5</v>
       </c>
@@ -2242,18 +2756,18 @@
       </c>
     </row>
     <row r="18" spans="1:15" ht="18" customHeight="1">
-      <c r="A18" s="11"/>
+      <c r="A18" s="13"/>
       <c r="B18" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" s="14"/>
+      <c r="C18" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="16"/>
+      <c r="E18" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="16"/>
       <c r="G18" s="6" t="s">
         <v>6</v>
       </c>
@@ -2262,18 +2776,18 @@
       </c>
     </row>
     <row r="19" spans="1:15" ht="18" customHeight="1">
-      <c r="A19" s="11"/>
+      <c r="A19" s="13"/>
       <c r="B19" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" s="14"/>
-      <c r="E19" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" s="14"/>
+      <c r="C19" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="16"/>
+      <c r="E19" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="16"/>
       <c r="G19" s="6" t="s">
         <v>6</v>
       </c>
@@ -2282,18 +2796,18 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="16.3">
-      <c r="A20" s="11"/>
+      <c r="A20" s="13"/>
       <c r="B20" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="F20" s="14"/>
+      <c r="C20" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" s="16"/>
+      <c r="E20" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F20" s="16"/>
       <c r="G20" s="8" t="s">
         <v>6</v>
       </c>
@@ -2302,18 +2816,18 @@
       </c>
     </row>
     <row r="21" spans="1:15" ht="16.3">
-      <c r="A21" s="11"/>
+      <c r="A21" s="13"/>
       <c r="B21" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21" s="14"/>
-      <c r="E21" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="14"/>
+      <c r="C21" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="16"/>
+      <c r="E21" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="16"/>
       <c r="G21" s="6" t="s">
         <v>6</v>
       </c>
@@ -2322,20 +2836,20 @@
       </c>
     </row>
     <row r="22" spans="1:15" ht="16.3">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="12" t="s">
         <v>31</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" s="14"/>
+      <c r="C22" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="16"/>
+      <c r="E22" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="16"/>
       <c r="G22" s="6" t="s">
         <v>6</v>
       </c>
@@ -2344,18 +2858,18 @@
       </c>
     </row>
     <row r="23" spans="1:15" ht="16.3">
-      <c r="A23" s="11"/>
+      <c r="A23" s="13"/>
       <c r="B23" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" s="14"/>
+      <c r="C23" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="16"/>
+      <c r="E23" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="16"/>
       <c r="G23" s="8" t="s">
         <v>6</v>
       </c>
@@ -2364,73 +2878,73 @@
       </c>
     </row>
     <row r="24" spans="1:15" ht="16.3">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="14"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="16"/>
     </row>
     <row r="25" spans="1:15" ht="16.3">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="C25" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="16.3">
+      <c r="A26" s="12"/>
+      <c r="B26" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="E26" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" ht="16.3">
-      <c r="A26" s="10"/>
-      <c r="B26" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>79</v>
-      </c>
       <c r="F26" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="16.3">
-      <c r="A27" s="11"/>
+      <c r="A27" s="13"/>
       <c r="B27" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C27" s="6">
         <v>250</v>
@@ -2452,9 +2966,9 @@
       </c>
     </row>
     <row r="28" spans="1:15" s="7" customFormat="1" ht="16.3">
-      <c r="A28" s="11"/>
+      <c r="A28" s="13"/>
       <c r="B28" s="6" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C28" s="6">
         <v>81</v>
@@ -2483,9 +2997,9 @@
       <c r="O28" s="5"/>
     </row>
     <row r="29" spans="1:15" ht="16.3">
-      <c r="A29" s="11"/>
+      <c r="A29" s="13"/>
       <c r="B29" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C29" s="6">
         <v>110</v>
@@ -2500,16 +3014,16 @@
         <v>120</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="16.3">
-      <c r="A30" s="11"/>
+      <c r="A30" s="13"/>
       <c r="B30" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C30" s="6">
         <v>1110</v>
@@ -2531,9 +3045,9 @@
       </c>
     </row>
     <row r="31" spans="1:15" s="5" customFormat="1" ht="16.3">
-      <c r="A31" s="11"/>
+      <c r="A31" s="13"/>
       <c r="B31" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C31" s="3">
         <v>0.66</v>
@@ -2548,10 +3062,10 @@
         <v>0.61</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
@@ -2562,9 +3076,9 @@
       <c r="O31" s="2"/>
     </row>
     <row r="32" spans="1:15" ht="16.3">
-      <c r="A32" s="11"/>
+      <c r="A32" s="13"/>
       <c r="B32" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C32" s="3">
         <v>0.78</v>
@@ -2579,16 +3093,16 @@
         <v>0.72</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="16.3">
-      <c r="A33" s="11"/>
+      <c r="A33" s="13"/>
       <c r="B33" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C33" s="6">
         <v>32</v>
@@ -2610,9 +3124,9 @@
       </c>
     </row>
     <row r="34" spans="1:15" ht="16.3">
-      <c r="A34" s="11"/>
+      <c r="A34" s="13"/>
       <c r="B34" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C34" s="4">
         <v>95</v>
@@ -2634,9 +3148,9 @@
       </c>
     </row>
     <row r="35" spans="1:15" ht="16.3">
-      <c r="A35" s="11"/>
+      <c r="A35" s="13"/>
       <c r="B35" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C35" s="4">
         <v>1297</v>
@@ -2658,9 +3172,9 @@
       </c>
     </row>
     <row r="36" spans="1:15" ht="16.3">
-      <c r="A36" s="11"/>
+      <c r="A36" s="13"/>
       <c r="B36" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C36" s="4">
         <v>997</v>
@@ -2682,9 +3196,9 @@
       </c>
     </row>
     <row r="37" spans="1:15" ht="16.3">
-      <c r="A37" s="11"/>
+      <c r="A37" s="13"/>
       <c r="B37" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C37" s="4">
         <v>250</v>
@@ -2707,7 +3221,7 @@
     </row>
     <row r="38" spans="1:15" ht="18" customHeight="1">
       <c r="A38" s="9" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="18" customHeight="1">
@@ -2748,6 +3262,46 @@
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:A37"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:H24"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A2:B2"/>
@@ -2764,46 +3318,6 @@
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:A37"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:H24"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="A16:A21"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E4:F4"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
